--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_281_R29.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_281_R29.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.339600000000001</v>
+        <v>9.194800000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>9.236599999999999</v>
+        <v>8.9574</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1029</v>
+        <v>0.2374</v>
       </c>
       <c r="G2" t="n">
         <v>8.1639</v>
@@ -610,13 +610,13 @@
         <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9823</v>
+        <v>0.8375</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7749</v>
+        <v>0.4957</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2074</v>
+        <v>0.3418</v>
       </c>
       <c r="V2" t="n">
         <v>0.4254</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.9728</v>
+        <v>4.8546</v>
       </c>
       <c r="E3" t="n">
-        <v>1.4596</v>
+        <v>2.0808</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5132</v>
+        <v>2.7738</v>
       </c>
       <c r="G3" t="n">
         <v>-0.2807</v>
@@ -688,13 +688,13 @@
         <v>2.7834</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3979</v>
+        <v>1.2797</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0633</v>
+        <v>0.6844</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3346</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="V3" t="n">
         <v>1.0722</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.051</v>
+        <v>1.9645</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4776</v>
+        <v>0.391</v>
       </c>
       <c r="F4" t="n">
         <v>1.5735</v>
@@ -766,10 +766,10 @@
         <v>3.0154</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8927</v>
+        <v>0.8061</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8575</v>
+        <v>0.771</v>
       </c>
       <c r="U4" t="n">
         <v>0.0351</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7301</v>
+        <v>1.2685</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1127</v>
+        <v>0.1232</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8428</v>
+        <v>1.1453</v>
       </c>
       <c r="G5" t="n">
         <v>0.5127</v>
@@ -844,13 +844,13 @@
         <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4784</v>
+        <v>0.06</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4402</v>
+        <v>-0.2043</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0382</v>
+        <v>0.2642</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0109</v>
+        <v>0.2922</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.33</v>
+        <v>-0.0941</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3191</v>
+        <v>0.3863</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3703</v>
@@ -922,13 +922,13 @@
         <v>0.4639</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1046</v>
+        <v>0.1986</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1494</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0448</v>
+        <v>0.112</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. BIRCH</t>
+          <t>M. JANTUNEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0553</v>
+        <v>0.019</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.2267</v>
+        <v>0.2537</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1714</v>
+        <v>-0.2347</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0553</v>
+        <v>-2.0975</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.1295</v>
+        <v>-0.8929</v>
       </c>
       <c r="I7" t="n">
-        <v>1.0741</v>
+        <v>-1.2046</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5148</v>
+        <v>-0.9171</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6988</v>
+        <v>0.7058</v>
       </c>
       <c r="L7" t="n">
-        <v>0.184</v>
+        <v>-1.6229</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5405</v>
+        <v>-1.1804</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4306</v>
+        <v>-1.5987</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8901</v>
+        <v>0.4183</v>
       </c>
       <c r="P7" t="n">
-        <v>-3.0154</v>
+        <v>2.5515</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.639</v>
+        <v>-0.232</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6237</v>
+        <v>2.7834</v>
       </c>
       <c r="S7" t="n">
-        <v>2.8014</v>
+        <v>0.2429</v>
       </c>
       <c r="T7" t="n">
-        <v>2.7131</v>
+        <v>0.3306</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0883</v>
+        <v>-0.0876</v>
       </c>
       <c r="V7" t="n">
-        <v>1.214</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W7" t="n">
-        <v>1.214</v>
+        <v>1.0722</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3075</v>
+        <v>-0.4083</v>
       </c>
       <c r="E8" t="n">
         <v>-0.224</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0834</v>
+        <v>-0.1842</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3896</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3141</v>
+        <v>0.2133</v>
       </c>
       <c r="T8" t="n">
         <v>0.007900000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3062</v>
+        <v>0.2054</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. JANTUNEN</t>
+          <t>M. BIRSEN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3492</v>
+        <v>-1.152</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0136</v>
+        <v>-1.6682</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3355</v>
+        <v>0.5162</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.0975</v>
+        <v>-1.9904</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8929</v>
+        <v>-0.3107</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2046</v>
+        <v>-1.6797</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9171</v>
+        <v>-1.4719</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7058</v>
+        <v>0.1008</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.6229</v>
+        <v>-1.5727</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1804</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.5987</v>
+        <v>-0.4116</v>
       </c>
       <c r="O9" t="n">
-        <v>0.4183</v>
+        <v>-0.107</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5515</v>
+        <v>0.4639</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.232</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7834</v>
+        <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1252</v>
+        <v>0.3745</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0633</v>
+        <v>0.0356</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1885</v>
+        <v>0.3389</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. BIRSEN</t>
+          <t>K. BIRCH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2871</v>
+        <v>-1.346</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.9041</v>
+        <v>-2.6854</v>
       </c>
       <c r="F10" t="n">
-        <v>0.617</v>
+        <v>1.3394</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.9904</v>
+        <v>-1.0553</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3107</v>
+        <v>-2.1295</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.6797</v>
+        <v>1.0741</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4719</v>
+        <v>-0.5148</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1008</v>
+        <v>-0.6988</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.5727</v>
+        <v>0.184</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5185999999999999</v>
+        <v>-0.5405</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4116</v>
+        <v>-1.4306</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.107</v>
+        <v>0.8901</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4639</v>
+        <v>-3.0154</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.232</v>
+        <v>-4.639</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2394</v>
+        <v>1.5107</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2003</v>
+        <v>1.2544</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4397</v>
+        <v>0.2563</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2365</v>
+        <v>-2.1693</v>
       </c>
       <c r="E11" t="n">
         <v>-0.8195</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.417</v>
+        <v>-1.3498</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1423</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.022</v>
+        <v>0.0452</v>
       </c>
       <c r="T11" t="n">
         <v>-0.0668</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0448</v>
+        <v>0.112</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0722</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.8843</v>
+        <v>-7.8084</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.1246</v>
+        <v>-6.1495</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7597</v>
+        <v>-1.6589</v>
       </c>
       <c r="G12" t="n">
         <v>-6.6456</v>
@@ -1390,13 +1390,13 @@
         <v>2.7834</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0609</v>
+        <v>0.0149</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7899</v>
+        <v>0.1852</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.271</v>
+        <v>-0.1702</v>
       </c>
       <c r="V12" t="n">
         <v>0.6778999999999999</v>
@@ -1423,22 +1423,22 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.9627</v>
+        <v>4.709600000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.5813999999999995</v>
+        <v>0.1654000000000018</v>
       </c>
       <c r="F13" t="n">
-        <v>4.5443</v>
+        <v>4.544300000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-8.224300000000001</v>
+        <v>-8.224299999999999</v>
       </c>
       <c r="H13" t="n">
         <v>-9.027100000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8027999999999986</v>
+        <v>0.8027999999999995</v>
       </c>
       <c r="J13" t="n">
         <v>-2.088500000000001</v>
@@ -1450,7 +1450,7 @@
         <v>-3.112699999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-6.135799999999999</v>
+        <v>-6.1358</v>
       </c>
       <c r="N13" t="n">
         <v>-10.0513</v>
@@ -1459,7 +1459,7 @@
         <v>3.9154</v>
       </c>
       <c r="P13" t="n">
-        <v>4.638999999999999</v>
+        <v>4.639</v>
       </c>
       <c r="Q13" t="n">
         <v>-12.7575</v>
@@ -1468,10 +1468,10 @@
         <v>17.3964</v>
       </c>
       <c r="S13" t="n">
-        <v>4.836699999999999</v>
+        <v>5.5834</v>
       </c>
       <c r="T13" t="n">
-        <v>2.8334</v>
+        <v>3.5802</v>
       </c>
       <c r="U13" t="n">
         <v>2.0032</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.606</v>
+        <v>3.9884</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3434</v>
+        <v>2.5793</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2626</v>
+        <v>1.4091</v>
       </c>
       <c r="G14" t="n">
         <v>0.453</v>
@@ -1546,13 +1546,13 @@
         <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8316</v>
+        <v>-0.4492</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8962</v>
+        <v>-0.6603</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0646</v>
+        <v>0.2111</v>
       </c>
       <c r="V14" t="n">
         <v>3.7527</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. FERNANDO</t>
+          <t>D. OSETKOWSKI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.7181</v>
+        <v>0.6973</v>
       </c>
       <c r="E15" t="n">
-        <v>0.723</v>
+        <v>0.6574</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9951</v>
+        <v>0.0399</v>
       </c>
       <c r="G15" t="n">
-        <v>4.7048</v>
+        <v>1.2816</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2529</v>
+        <v>0.9737</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4518</v>
+        <v>0.3079</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7577</v>
+        <v>0.4631</v>
       </c>
       <c r="K15" t="n">
-        <v>3.7209</v>
+        <v>0.306</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0368</v>
+        <v>0.1571</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.8185</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5321</v>
+        <v>0.6677999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>0.415</v>
+        <v>0.1507</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.7112</v>
+        <v>1.3917</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.871</v>
+        <v>-0.232</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4746</v>
+        <v>-0.3677</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8363</v>
+        <v>-0.1098</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6383</v>
+        <v>-0.2579</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.7501</v>
+        <v>-1.6083</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.7501</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. WASHINGTON</t>
+          <t>B. FERNANDO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.624</v>
+        <v>0.5062</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.239</v>
+        <v>-0.4565</v>
       </c>
       <c r="F16" t="n">
-        <v>1.863</v>
+        <v>0.9628</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0357</v>
+        <v>4.7048</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5939</v>
+        <v>4.2529</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.6296</v>
+        <v>0.4518</v>
       </c>
       <c r="J16" t="n">
-        <v>0.2754</v>
+        <v>3.7577</v>
       </c>
       <c r="K16" t="n">
-        <v>1.691</v>
+        <v>3.7209</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.4155</v>
+        <v>0.0368</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3111</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.097</v>
+        <v>0.5321</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.214</v>
+        <v>0.415</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9278</v>
+        <v>-3.7112</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.5515</v>
+        <v>-4.871</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5153</v>
+        <v>1.2628</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0351</v>
+        <v>0.6567</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5505</v>
+        <v>0.606</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0722</v>
+        <v>-1.7501</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. MILTON</t>
+          <t>D. WASHINGTON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2491</v>
+        <v>0.4674</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0005</v>
+        <v>-1.4749</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7514</v>
+        <v>1.9423</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7408</v>
+        <v>-0.0357</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2857</v>
+        <v>1.5939</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4551</v>
+        <v>-1.6296</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3764</v>
+        <v>0.2754</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3396</v>
+        <v>1.691</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0368</v>
+        <v>-1.4155</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3644</v>
+        <v>-0.3111</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0539</v>
+        <v>-0.097</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4183</v>
+        <v>-0.214</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9278</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8834</v>
+        <v>0.3587</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4481</v>
+        <v>-0.2711</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4353</v>
+        <v>0.6297</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5361</v>
+        <v>1.0722</v>
       </c>
       <c r="W17" t="n">
         <v>1.0722</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. OSETKOWSKI</t>
+          <t>S. MILTON</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3794</v>
+        <v>0.3727</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6574</v>
+        <v>1.0005</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.0368</v>
+        <v>-0.6278</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2816</v>
+        <v>0.7408</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9737</v>
+        <v>0.2857</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3079</v>
+        <v>0.4551</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4631</v>
+        <v>0.3764</v>
       </c>
       <c r="K18" t="n">
-        <v>0.306</v>
+        <v>0.3396</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1571</v>
+        <v>0.0368</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8185</v>
+        <v>0.3644</v>
       </c>
       <c r="N18" t="n">
-        <v>0.6677999999999999</v>
+        <v>-0.0539</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1507</v>
+        <v>0.4183</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4444</v>
+        <v>-0.7598</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1098</v>
+        <v>-0.4481</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.3346</v>
+        <v>-0.3117</v>
       </c>
       <c r="V18" t="n">
+        <v>-0.5361</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.0722</v>
+      </c>
+      <c r="X18" t="n">
         <v>-1.6083</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0.5361</v>
-      </c>
-      <c r="X18" t="n">
-        <v>-2.1444</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1922</v>
+        <v>-0.0133</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8717</v>
+        <v>-0.3999</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3205</v>
+        <v>0.3866</v>
       </c>
       <c r="G19" t="n">
         <v>1.5794</v>
@@ -1936,13 +1936,13 @@
         <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1839</v>
+        <v>-0.005</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4481</v>
+        <v>0.0237</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7358</v>
+        <v>-0.0288</v>
       </c>
       <c r="V19" t="n">
         <v>-1.3558</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5716</v>
+        <v>-0.9698</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7111</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8605</v>
+        <v>-0.3766</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8636</v>
@@ -2014,13 +2014,13 @@
         <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1322</v>
+        <v>0.7341</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1098</v>
+        <v>0.0081</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2421</v>
+        <v>0.726</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0722</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5915</v>
+        <v>-1.0918</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7145</v>
+        <v>-0.5965</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.877</v>
+        <v>-0.4953</v>
       </c>
       <c r="G21" t="n">
         <v>0.7374000000000001</v>
@@ -2092,13 +2092,13 @@
         <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3469</v>
+        <v>-0.8472</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8215</v>
+        <v>-0.7035</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5254</v>
+        <v>-0.1436</v>
       </c>
       <c r="V21" t="n">
         <v>-1.214</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.041</v>
+        <v>-1.6313</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1136</v>
+        <v>-0.9957</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9274</v>
+        <v>-0.6357</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2236</v>
@@ -2170,13 +2170,13 @@
         <v>0.9278</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.673</v>
+        <v>-0.2634</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4481</v>
+        <v>-0.3301</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2249</v>
+        <v>0.0668</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3842</v>
+        <v>-2.3569</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.6187</v>
+        <v>-4.2648</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2345</v>
+        <v>1.9079</v>
       </c>
       <c r="G23" t="n">
         <v>0.8502999999999999</v>
@@ -2248,13 +2248,13 @@
         <v>0.9278</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.5955</v>
+        <v>-0.5682</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5228</v>
+        <v>-0.1689</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.0728</v>
+        <v>-0.3993</v>
       </c>
       <c r="V23" t="n">
         <v>1.0722</v>
@@ -2281,25 +2281,25 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.9627</v>
+        <v>-0.03110000000000035</v>
       </c>
       <c r="E24" t="n">
         <v>-4.5443</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5815999999999997</v>
+        <v>4.513199999999999</v>
       </c>
       <c r="G24" t="n">
         <v>8.224399999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>9.027100000000001</v>
+        <v>9.027099999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8028</v>
+        <v>-0.8027999999999995</v>
       </c>
       <c r="J24" t="n">
-        <v>6.1359</v>
+        <v>6.135900000000001</v>
       </c>
       <c r="K24" t="n">
         <v>10.0515</v>
@@ -2326,13 +2326,13 @@
         <v>12.7575</v>
       </c>
       <c r="S24" t="n">
-        <v>-4.8366</v>
+        <v>-0.9049</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.0032</v>
+        <v>-2.0033</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.8333</v>
+        <v>1.0983</v>
       </c>
       <c r="V24" t="n">
         <v>-2.7116</v>
